--- a/GUA/IPPU/A1_Outputs/A-O_AR_Projections_COMPLETED.xlsx
+++ b/GUA/IPPU/A1_Outputs/A-O_AR_Projections_COMPLETED.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="104">
   <si>
     <t>Tech</t>
   </si>
@@ -39,18 +39,108 @@
     <t>RAW_MAT_CEM</t>
   </si>
   <si>
+    <t>IMP_STOR</t>
+  </si>
+  <si>
+    <t>LIME_CAL_PROD</t>
+  </si>
+  <si>
+    <t>LIME_DOL_PROD</t>
+  </si>
+  <si>
+    <t>GLASS_PROD</t>
+  </si>
+  <si>
+    <t>CARBONATE_CERAMICS</t>
+  </si>
+  <si>
+    <t>CARBONATE_ASH</t>
+  </si>
+  <si>
+    <t>IRON_STEEL</t>
+  </si>
+  <si>
+    <t>PROD_FERRO</t>
+  </si>
+  <si>
+    <t>LUBRI_OILS</t>
+  </si>
+  <si>
+    <t>PARAFFIN</t>
+  </si>
+  <si>
+    <t>REFR_AC_HFC32</t>
+  </si>
+  <si>
+    <t>REFR_AC_HFC125</t>
+  </si>
+  <si>
+    <t>REFR_AC_HFC134a</t>
+  </si>
+  <si>
+    <t>REFR_AC_HFC143a</t>
+  </si>
+  <si>
     <t>Supply of raw material for clinker</t>
   </si>
   <si>
     <t>Supply of raw material for cement</t>
   </si>
   <si>
+    <t>Imports or storage of Clinker</t>
+  </si>
+  <si>
+    <t>Lime production calcitic</t>
+  </si>
+  <si>
+    <t>Lime production dolomitic</t>
+  </si>
+  <si>
+    <t>Glass production</t>
+  </si>
+  <si>
+    <t>Carbonate ceramics</t>
+  </si>
+  <si>
+    <t>Carbonate soda ash</t>
+  </si>
+  <si>
+    <t>Iron and Steel production</t>
+  </si>
+  <si>
+    <t>Ferroalloy production</t>
+  </si>
+  <si>
+    <t>Use of Lubricants Oils</t>
+  </si>
+  <si>
+    <t>Use of Paraffin Wax</t>
+  </si>
+  <si>
+    <t>Refrigeration and air conditioning HFC32</t>
+  </si>
+  <si>
+    <t>Refrigeration and air conditioning HFC125</t>
+  </si>
+  <si>
+    <t>Refrigeration and air conditioning HFC134a</t>
+  </si>
+  <si>
+    <t>Refrigeration and air conditioning HFC143a</t>
+  </si>
+  <si>
+    <t>CLK_PROD</t>
+  </si>
+  <si>
     <t>Raw materials for clinker</t>
   </si>
   <si>
     <t>Raw materials for cement</t>
   </si>
   <si>
+    <t>Clinker production</t>
+  </si>
+  <si>
     <t>OutputActivityRatio</t>
   </si>
   <si>
@@ -66,28 +156,178 @@
     <t>Cement production</t>
   </si>
   <si>
-    <t>CLK_PROD</t>
-  </si>
-  <si>
     <t>CEM_PROD</t>
   </si>
   <si>
-    <t>Clinker production</t>
-  </si>
-  <si>
     <t>InputActivityRatio</t>
   </si>
   <si>
-    <t>T5CEM_PRODCEM_PROD</t>
-  </si>
-  <si>
-    <t>Demand Cement production for Cement production</t>
-  </si>
-  <si>
-    <t>E5_CEM_PRODCEM_PROD</t>
-  </si>
-  <si>
-    <t>Demand Cement production Cement production</t>
+    <t>T5CEM_PRODIND</t>
+  </si>
+  <si>
+    <t>T5LIME_CAL_PRODIPPU</t>
+  </si>
+  <si>
+    <t>T5LIME_DOL_PRODIPPU</t>
+  </si>
+  <si>
+    <t>T5GLASS_PRODIPPU</t>
+  </si>
+  <si>
+    <t>T5CARBONATE_CERAMICSIPPU</t>
+  </si>
+  <si>
+    <t>T5CARBONATE_ASHIPPU</t>
+  </si>
+  <si>
+    <t>T5IRON_STEELIPPU</t>
+  </si>
+  <si>
+    <t>T5PROD_FERROIPPU</t>
+  </si>
+  <si>
+    <t>T5LUBRI_OILSIPPU</t>
+  </si>
+  <si>
+    <t>T5PARAFFINIPPU</t>
+  </si>
+  <si>
+    <t>T5REFR_AC_HFC32IPPU</t>
+  </si>
+  <si>
+    <t>T5REFR_AC_HFC125IPPU</t>
+  </si>
+  <si>
+    <t>T5REFR_AC_HFC134aIPPU</t>
+  </si>
+  <si>
+    <t>T5REFR_AC_HFC143aIPPU</t>
+  </si>
+  <si>
+    <t>Demand Cement production for Industrial</t>
+  </si>
+  <si>
+    <t>Demand Lime production calcitic for Industrial Processes</t>
+  </si>
+  <si>
+    <t>Demand Lime production dolomitic for Industrial Processes</t>
+  </si>
+  <si>
+    <t>Demand Glass production for Industrial Processes</t>
+  </si>
+  <si>
+    <t>Demand Carbonate ceramics for Industrial Processes</t>
+  </si>
+  <si>
+    <t>Demand Carbonate soda ash for Industrial Processes</t>
+  </si>
+  <si>
+    <t>Demand Iron and Steel production for Industrial Processes</t>
+  </si>
+  <si>
+    <t>Demand Ferroalloy production for Industrial Processes</t>
+  </si>
+  <si>
+    <t>Demand Use of Lubricants Oils for Industrial Processes</t>
+  </si>
+  <si>
+    <t>Demand Use of Paraffin Wax for Industrial Processes</t>
+  </si>
+  <si>
+    <t>Demand Refrigeration and air conditioning HFC32 for Industrial Processes</t>
+  </si>
+  <si>
+    <t>Demand Refrigeration and air conditioning HFC125 for Industrial Processes</t>
+  </si>
+  <si>
+    <t>Demand Refrigeration and air conditioning HFC134a for Industrial Processes</t>
+  </si>
+  <si>
+    <t>Demand Refrigeration and air conditioning HFC143a for Industrial Processes</t>
+  </si>
+  <si>
+    <t>E5INDCEM_PROD</t>
+  </si>
+  <si>
+    <t>E5IPPULIME_CAL_PROD</t>
+  </si>
+  <si>
+    <t>E5IPPULIME_DOL_PROD</t>
+  </si>
+  <si>
+    <t>E5IPPUGLASS_PROD</t>
+  </si>
+  <si>
+    <t>E5IPPUCARBONATE_CERAMICS</t>
+  </si>
+  <si>
+    <t>E5IPPUCARBONATE_ASH</t>
+  </si>
+  <si>
+    <t>E5IPPUIRON_STEEL</t>
+  </si>
+  <si>
+    <t>E5IPPUPROD_FERRO</t>
+  </si>
+  <si>
+    <t>E5IPPULUBRI_OILS</t>
+  </si>
+  <si>
+    <t>E5IPPUPARAFFIN</t>
+  </si>
+  <si>
+    <t>E5IPPUREFR_AC_HFC32</t>
+  </si>
+  <si>
+    <t>E5IPPUREFR_AC_HFC125</t>
+  </si>
+  <si>
+    <t>E5IPPUREFR_AC_HFC134a</t>
+  </si>
+  <si>
+    <t>E5IPPUREFR_AC_HFC143a</t>
+  </si>
+  <si>
+    <t>Demand Industrial Cement production</t>
+  </si>
+  <si>
+    <t>Demand Industrial Processes Lime production calcitic</t>
+  </si>
+  <si>
+    <t>Demand Industrial Processes Lime production dolomitic</t>
+  </si>
+  <si>
+    <t>Demand Industrial Processes Glass production</t>
+  </si>
+  <si>
+    <t>Demand Industrial Processes Carbonate ceramics</t>
+  </si>
+  <si>
+    <t>Demand Industrial Processes Carbonate soda ash</t>
+  </si>
+  <si>
+    <t>Demand Industrial Processes Iron and Steel production</t>
+  </si>
+  <si>
+    <t>Demand Industrial Processes Ferroalloy production</t>
+  </si>
+  <si>
+    <t>Demand Industrial Processes Use of Lubricants Oils</t>
+  </si>
+  <si>
+    <t>Demand Industrial Processes Use of Paraffin Wax</t>
+  </si>
+  <si>
+    <t>Demand Industrial Processes Refrigeration and air conditioning HFC32</t>
+  </si>
+  <si>
+    <t>Demand Industrial Processes Refrigeration and air conditioning HFC125</t>
+  </si>
+  <si>
+    <t>Demand Industrial Processes Refrigeration and air conditioning HFC134a</t>
+  </si>
+  <si>
+    <t>Demand Industrial Processes Refrigeration and air conditioning HFC143a</t>
   </si>
 </sst>
 </file>
@@ -445,7 +685,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AL3"/>
+  <dimension ref="A1:AL17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:38">
@@ -569,16 +809,16 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
         <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -685,114 +925,1738 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
       </c>
       <c r="D3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+      <c r="N3">
+        <v>1</v>
+      </c>
+      <c r="O3">
+        <v>1</v>
+      </c>
+      <c r="P3">
+        <v>1</v>
+      </c>
+      <c r="Q3">
+        <v>1</v>
+      </c>
+      <c r="R3">
+        <v>1</v>
+      </c>
+      <c r="S3">
+        <v>1</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
+      </c>
+      <c r="U3">
+        <v>1</v>
+      </c>
+      <c r="V3">
+        <v>1</v>
+      </c>
+      <c r="W3">
+        <v>1</v>
+      </c>
+      <c r="X3">
+        <v>1</v>
+      </c>
+      <c r="Y3">
+        <v>1</v>
+      </c>
+      <c r="Z3">
+        <v>1</v>
+      </c>
+      <c r="AA3">
+        <v>1</v>
+      </c>
+      <c r="AB3">
+        <v>1</v>
+      </c>
+      <c r="AC3">
+        <v>1</v>
+      </c>
+      <c r="AD3">
+        <v>1</v>
+      </c>
+      <c r="AE3">
+        <v>1</v>
+      </c>
+      <c r="AF3">
+        <v>1</v>
+      </c>
+      <c r="AG3">
+        <v>1</v>
+      </c>
+      <c r="AH3">
+        <v>1</v>
+      </c>
+      <c r="AI3">
+        <v>1</v>
+      </c>
+      <c r="AJ3">
+        <v>1</v>
+      </c>
+      <c r="AK3">
+        <v>1</v>
+      </c>
+      <c r="AL3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:38">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E4" t="s">
+        <v>41</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+      <c r="N4">
+        <v>1</v>
+      </c>
+      <c r="O4">
+        <v>1</v>
+      </c>
+      <c r="P4">
+        <v>1</v>
+      </c>
+      <c r="Q4">
+        <v>1</v>
+      </c>
+      <c r="R4">
+        <v>1</v>
+      </c>
+      <c r="S4">
+        <v>1</v>
+      </c>
+      <c r="T4">
+        <v>1</v>
+      </c>
+      <c r="U4">
+        <v>1</v>
+      </c>
+      <c r="V4">
+        <v>1</v>
+      </c>
+      <c r="W4">
+        <v>1</v>
+      </c>
+      <c r="X4">
+        <v>1</v>
+      </c>
+      <c r="Y4">
+        <v>1</v>
+      </c>
+      <c r="Z4">
+        <v>1</v>
+      </c>
+      <c r="AA4">
+        <v>1</v>
+      </c>
+      <c r="AB4">
+        <v>1</v>
+      </c>
+      <c r="AC4">
+        <v>1</v>
+      </c>
+      <c r="AD4">
+        <v>1</v>
+      </c>
+      <c r="AE4">
+        <v>1</v>
+      </c>
+      <c r="AF4">
+        <v>1</v>
+      </c>
+      <c r="AG4">
+        <v>1</v>
+      </c>
+      <c r="AH4">
+        <v>1</v>
+      </c>
+      <c r="AI4">
+        <v>1</v>
+      </c>
+      <c r="AJ4">
+        <v>1</v>
+      </c>
+      <c r="AK4">
+        <v>1</v>
+      </c>
+      <c r="AL4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:38">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+      <c r="N5">
+        <v>1</v>
+      </c>
+      <c r="O5">
+        <v>1</v>
+      </c>
+      <c r="P5">
+        <v>1</v>
+      </c>
+      <c r="Q5">
+        <v>1</v>
+      </c>
+      <c r="R5">
+        <v>1</v>
+      </c>
+      <c r="S5">
+        <v>1</v>
+      </c>
+      <c r="T5">
+        <v>1</v>
+      </c>
+      <c r="U5">
+        <v>1</v>
+      </c>
+      <c r="V5">
+        <v>1</v>
+      </c>
+      <c r="W5">
+        <v>1</v>
+      </c>
+      <c r="X5">
+        <v>1</v>
+      </c>
+      <c r="Y5">
+        <v>1</v>
+      </c>
+      <c r="Z5">
+        <v>1</v>
+      </c>
+      <c r="AA5">
+        <v>1</v>
+      </c>
+      <c r="AB5">
+        <v>1</v>
+      </c>
+      <c r="AC5">
+        <v>1</v>
+      </c>
+      <c r="AD5">
+        <v>1</v>
+      </c>
+      <c r="AE5">
+        <v>1</v>
+      </c>
+      <c r="AF5">
+        <v>1</v>
+      </c>
+      <c r="AG5">
+        <v>1</v>
+      </c>
+      <c r="AH5">
+        <v>1</v>
+      </c>
+      <c r="AI5">
+        <v>1</v>
+      </c>
+      <c r="AJ5">
+        <v>1</v>
+      </c>
+      <c r="AK5">
+        <v>1</v>
+      </c>
+      <c r="AL5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:38">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="P6">
+        <v>1</v>
+      </c>
+      <c r="Q6">
+        <v>1</v>
+      </c>
+      <c r="R6">
+        <v>1</v>
+      </c>
+      <c r="S6">
+        <v>1</v>
+      </c>
+      <c r="T6">
+        <v>1</v>
+      </c>
+      <c r="U6">
+        <v>1</v>
+      </c>
+      <c r="V6">
+        <v>1</v>
+      </c>
+      <c r="W6">
+        <v>1</v>
+      </c>
+      <c r="X6">
+        <v>1</v>
+      </c>
+      <c r="Y6">
+        <v>1</v>
+      </c>
+      <c r="Z6">
+        <v>1</v>
+      </c>
+      <c r="AA6">
+        <v>1</v>
+      </c>
+      <c r="AB6">
+        <v>1</v>
+      </c>
+      <c r="AC6">
+        <v>1</v>
+      </c>
+      <c r="AD6">
+        <v>1</v>
+      </c>
+      <c r="AE6">
+        <v>1</v>
+      </c>
+      <c r="AF6">
+        <v>1</v>
+      </c>
+      <c r="AG6">
+        <v>1</v>
+      </c>
+      <c r="AH6">
+        <v>1</v>
+      </c>
+      <c r="AI6">
+        <v>1</v>
+      </c>
+      <c r="AJ6">
+        <v>1</v>
+      </c>
+      <c r="AK6">
+        <v>1</v>
+      </c>
+      <c r="AL6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:38">
+      <c r="A7" t="s">
         <v>10</v>
       </c>
-      <c r="E3" t="s">
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+      <c r="N7">
+        <v>1</v>
+      </c>
+      <c r="O7">
+        <v>1</v>
+      </c>
+      <c r="P7">
+        <v>1</v>
+      </c>
+      <c r="Q7">
+        <v>1</v>
+      </c>
+      <c r="R7">
+        <v>1</v>
+      </c>
+      <c r="S7">
+        <v>1</v>
+      </c>
+      <c r="T7">
+        <v>1</v>
+      </c>
+      <c r="U7">
+        <v>1</v>
+      </c>
+      <c r="V7">
+        <v>1</v>
+      </c>
+      <c r="W7">
+        <v>1</v>
+      </c>
+      <c r="X7">
+        <v>1</v>
+      </c>
+      <c r="Y7">
+        <v>1</v>
+      </c>
+      <c r="Z7">
+        <v>1</v>
+      </c>
+      <c r="AA7">
+        <v>1</v>
+      </c>
+      <c r="AB7">
+        <v>1</v>
+      </c>
+      <c r="AC7">
+        <v>1</v>
+      </c>
+      <c r="AD7">
+        <v>1</v>
+      </c>
+      <c r="AE7">
+        <v>1</v>
+      </c>
+      <c r="AF7">
+        <v>1</v>
+      </c>
+      <c r="AG7">
+        <v>1</v>
+      </c>
+      <c r="AH7">
+        <v>1</v>
+      </c>
+      <c r="AI7">
+        <v>1</v>
+      </c>
+      <c r="AJ7">
+        <v>1</v>
+      </c>
+      <c r="AK7">
+        <v>1</v>
+      </c>
+      <c r="AL7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:38">
+      <c r="A8" t="s">
         <v>11</v>
       </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-      <c r="N3">
-        <v>1</v>
-      </c>
-      <c r="O3">
-        <v>1</v>
-      </c>
-      <c r="P3">
-        <v>1</v>
-      </c>
-      <c r="Q3">
-        <v>1</v>
-      </c>
-      <c r="R3">
-        <v>1</v>
-      </c>
-      <c r="S3">
-        <v>1</v>
-      </c>
-      <c r="T3">
-        <v>1</v>
-      </c>
-      <c r="U3">
-        <v>1</v>
-      </c>
-      <c r="V3">
-        <v>1</v>
-      </c>
-      <c r="W3">
-        <v>1</v>
-      </c>
-      <c r="X3">
-        <v>1</v>
-      </c>
-      <c r="Y3">
-        <v>1</v>
-      </c>
-      <c r="Z3">
-        <v>1</v>
-      </c>
-      <c r="AA3">
-        <v>1</v>
-      </c>
-      <c r="AB3">
-        <v>1</v>
-      </c>
-      <c r="AC3">
-        <v>1</v>
-      </c>
-      <c r="AD3">
-        <v>1</v>
-      </c>
-      <c r="AE3">
-        <v>1</v>
-      </c>
-      <c r="AF3">
-        <v>1</v>
-      </c>
-      <c r="AG3">
-        <v>1</v>
-      </c>
-      <c r="AH3">
-        <v>1</v>
-      </c>
-      <c r="AI3">
-        <v>1</v>
-      </c>
-      <c r="AJ3">
-        <v>1</v>
-      </c>
-      <c r="AK3">
-        <v>1</v>
-      </c>
-      <c r="AL3">
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <v>1</v>
+      </c>
+      <c r="N8">
+        <v>1</v>
+      </c>
+      <c r="O8">
+        <v>1</v>
+      </c>
+      <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="Q8">
+        <v>1</v>
+      </c>
+      <c r="R8">
+        <v>1</v>
+      </c>
+      <c r="S8">
+        <v>1</v>
+      </c>
+      <c r="T8">
+        <v>1</v>
+      </c>
+      <c r="U8">
+        <v>1</v>
+      </c>
+      <c r="V8">
+        <v>1</v>
+      </c>
+      <c r="W8">
+        <v>1</v>
+      </c>
+      <c r="X8">
+        <v>1</v>
+      </c>
+      <c r="Y8">
+        <v>1</v>
+      </c>
+      <c r="Z8">
+        <v>1</v>
+      </c>
+      <c r="AA8">
+        <v>1</v>
+      </c>
+      <c r="AB8">
+        <v>1</v>
+      </c>
+      <c r="AC8">
+        <v>1</v>
+      </c>
+      <c r="AD8">
+        <v>1</v>
+      </c>
+      <c r="AE8">
+        <v>1</v>
+      </c>
+      <c r="AF8">
+        <v>1</v>
+      </c>
+      <c r="AG8">
+        <v>1</v>
+      </c>
+      <c r="AH8">
+        <v>1</v>
+      </c>
+      <c r="AI8">
+        <v>1</v>
+      </c>
+      <c r="AJ8">
+        <v>1</v>
+      </c>
+      <c r="AK8">
+        <v>1</v>
+      </c>
+      <c r="AL8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:38">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>1</v>
+      </c>
+      <c r="M9">
+        <v>1</v>
+      </c>
+      <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="O9">
+        <v>1</v>
+      </c>
+      <c r="P9">
+        <v>1</v>
+      </c>
+      <c r="Q9">
+        <v>1</v>
+      </c>
+      <c r="R9">
+        <v>1</v>
+      </c>
+      <c r="S9">
+        <v>1</v>
+      </c>
+      <c r="T9">
+        <v>1</v>
+      </c>
+      <c r="U9">
+        <v>1</v>
+      </c>
+      <c r="V9">
+        <v>1</v>
+      </c>
+      <c r="W9">
+        <v>1</v>
+      </c>
+      <c r="X9">
+        <v>1</v>
+      </c>
+      <c r="Y9">
+        <v>1</v>
+      </c>
+      <c r="Z9">
+        <v>1</v>
+      </c>
+      <c r="AA9">
+        <v>1</v>
+      </c>
+      <c r="AB9">
+        <v>1</v>
+      </c>
+      <c r="AC9">
+        <v>1</v>
+      </c>
+      <c r="AD9">
+        <v>1</v>
+      </c>
+      <c r="AE9">
+        <v>1</v>
+      </c>
+      <c r="AF9">
+        <v>1</v>
+      </c>
+      <c r="AG9">
+        <v>1</v>
+      </c>
+      <c r="AH9">
+        <v>1</v>
+      </c>
+      <c r="AI9">
+        <v>1</v>
+      </c>
+      <c r="AJ9">
+        <v>1</v>
+      </c>
+      <c r="AK9">
+        <v>1</v>
+      </c>
+      <c r="AL9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:38">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" t="s">
+        <v>41</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="M10">
+        <v>1</v>
+      </c>
+      <c r="N10">
+        <v>1</v>
+      </c>
+      <c r="O10">
+        <v>1</v>
+      </c>
+      <c r="P10">
+        <v>1</v>
+      </c>
+      <c r="Q10">
+        <v>1</v>
+      </c>
+      <c r="R10">
+        <v>1</v>
+      </c>
+      <c r="S10">
+        <v>1</v>
+      </c>
+      <c r="T10">
+        <v>1</v>
+      </c>
+      <c r="U10">
+        <v>1</v>
+      </c>
+      <c r="V10">
+        <v>1</v>
+      </c>
+      <c r="W10">
+        <v>1</v>
+      </c>
+      <c r="X10">
+        <v>1</v>
+      </c>
+      <c r="Y10">
+        <v>1</v>
+      </c>
+      <c r="Z10">
+        <v>1</v>
+      </c>
+      <c r="AA10">
+        <v>1</v>
+      </c>
+      <c r="AB10">
+        <v>1</v>
+      </c>
+      <c r="AC10">
+        <v>1</v>
+      </c>
+      <c r="AD10">
+        <v>1</v>
+      </c>
+      <c r="AE10">
+        <v>1</v>
+      </c>
+      <c r="AF10">
+        <v>1</v>
+      </c>
+      <c r="AG10">
+        <v>1</v>
+      </c>
+      <c r="AH10">
+        <v>1</v>
+      </c>
+      <c r="AI10">
+        <v>1</v>
+      </c>
+      <c r="AJ10">
+        <v>1</v>
+      </c>
+      <c r="AK10">
+        <v>1</v>
+      </c>
+      <c r="AL10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:38">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" t="s">
+        <v>41</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
+      <c r="M11">
+        <v>1</v>
+      </c>
+      <c r="N11">
+        <v>1</v>
+      </c>
+      <c r="O11">
+        <v>1</v>
+      </c>
+      <c r="P11">
+        <v>1</v>
+      </c>
+      <c r="Q11">
+        <v>1</v>
+      </c>
+      <c r="R11">
+        <v>1</v>
+      </c>
+      <c r="S11">
+        <v>1</v>
+      </c>
+      <c r="T11">
+        <v>1</v>
+      </c>
+      <c r="U11">
+        <v>1</v>
+      </c>
+      <c r="V11">
+        <v>1</v>
+      </c>
+      <c r="W11">
+        <v>1</v>
+      </c>
+      <c r="X11">
+        <v>1</v>
+      </c>
+      <c r="Y11">
+        <v>1</v>
+      </c>
+      <c r="Z11">
+        <v>1</v>
+      </c>
+      <c r="AA11">
+        <v>1</v>
+      </c>
+      <c r="AB11">
+        <v>1</v>
+      </c>
+      <c r="AC11">
+        <v>1</v>
+      </c>
+      <c r="AD11">
+        <v>1</v>
+      </c>
+      <c r="AE11">
+        <v>1</v>
+      </c>
+      <c r="AF11">
+        <v>1</v>
+      </c>
+      <c r="AG11">
+        <v>1</v>
+      </c>
+      <c r="AH11">
+        <v>1</v>
+      </c>
+      <c r="AI11">
+        <v>1</v>
+      </c>
+      <c r="AJ11">
+        <v>1</v>
+      </c>
+      <c r="AK11">
+        <v>1</v>
+      </c>
+      <c r="AL11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:38">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" t="s">
+        <v>41</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
+      <c r="M12">
+        <v>1</v>
+      </c>
+      <c r="N12">
+        <v>1</v>
+      </c>
+      <c r="O12">
+        <v>1</v>
+      </c>
+      <c r="P12">
+        <v>1</v>
+      </c>
+      <c r="Q12">
+        <v>1</v>
+      </c>
+      <c r="R12">
+        <v>1</v>
+      </c>
+      <c r="S12">
+        <v>1</v>
+      </c>
+      <c r="T12">
+        <v>1</v>
+      </c>
+      <c r="U12">
+        <v>1</v>
+      </c>
+      <c r="V12">
+        <v>1</v>
+      </c>
+      <c r="W12">
+        <v>1</v>
+      </c>
+      <c r="X12">
+        <v>1</v>
+      </c>
+      <c r="Y12">
+        <v>1</v>
+      </c>
+      <c r="Z12">
+        <v>1</v>
+      </c>
+      <c r="AA12">
+        <v>1</v>
+      </c>
+      <c r="AB12">
+        <v>1</v>
+      </c>
+      <c r="AC12">
+        <v>1</v>
+      </c>
+      <c r="AD12">
+        <v>1</v>
+      </c>
+      <c r="AE12">
+        <v>1</v>
+      </c>
+      <c r="AF12">
+        <v>1</v>
+      </c>
+      <c r="AG12">
+        <v>1</v>
+      </c>
+      <c r="AH12">
+        <v>1</v>
+      </c>
+      <c r="AI12">
+        <v>1</v>
+      </c>
+      <c r="AJ12">
+        <v>1</v>
+      </c>
+      <c r="AK12">
+        <v>1</v>
+      </c>
+      <c r="AL12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:38">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" t="s">
+        <v>32</v>
+      </c>
+      <c r="E13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+      <c r="K13">
+        <v>1</v>
+      </c>
+      <c r="L13">
+        <v>1</v>
+      </c>
+      <c r="M13">
+        <v>1</v>
+      </c>
+      <c r="N13">
+        <v>1</v>
+      </c>
+      <c r="O13">
+        <v>1</v>
+      </c>
+      <c r="P13">
+        <v>1</v>
+      </c>
+      <c r="Q13">
+        <v>1</v>
+      </c>
+      <c r="R13">
+        <v>1</v>
+      </c>
+      <c r="S13">
+        <v>1</v>
+      </c>
+      <c r="T13">
+        <v>1</v>
+      </c>
+      <c r="U13">
+        <v>1</v>
+      </c>
+      <c r="V13">
+        <v>1</v>
+      </c>
+      <c r="W13">
+        <v>1</v>
+      </c>
+      <c r="X13">
+        <v>1</v>
+      </c>
+      <c r="Y13">
+        <v>1</v>
+      </c>
+      <c r="Z13">
+        <v>1</v>
+      </c>
+      <c r="AA13">
+        <v>1</v>
+      </c>
+      <c r="AB13">
+        <v>1</v>
+      </c>
+      <c r="AC13">
+        <v>1</v>
+      </c>
+      <c r="AD13">
+        <v>1</v>
+      </c>
+      <c r="AE13">
+        <v>1</v>
+      </c>
+      <c r="AF13">
+        <v>1</v>
+      </c>
+      <c r="AG13">
+        <v>1</v>
+      </c>
+      <c r="AH13">
+        <v>1</v>
+      </c>
+      <c r="AI13">
+        <v>1</v>
+      </c>
+      <c r="AJ13">
+        <v>1</v>
+      </c>
+      <c r="AK13">
+        <v>1</v>
+      </c>
+      <c r="AL13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:38">
+      <c r="A14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" t="s">
+        <v>33</v>
+      </c>
+      <c r="E14" t="s">
+        <v>41</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="K14">
+        <v>1</v>
+      </c>
+      <c r="L14">
+        <v>1</v>
+      </c>
+      <c r="M14">
+        <v>1</v>
+      </c>
+      <c r="N14">
+        <v>1</v>
+      </c>
+      <c r="O14">
+        <v>1</v>
+      </c>
+      <c r="P14">
+        <v>1</v>
+      </c>
+      <c r="Q14">
+        <v>1</v>
+      </c>
+      <c r="R14">
+        <v>1</v>
+      </c>
+      <c r="S14">
+        <v>1</v>
+      </c>
+      <c r="T14">
+        <v>1</v>
+      </c>
+      <c r="U14">
+        <v>1</v>
+      </c>
+      <c r="V14">
+        <v>1</v>
+      </c>
+      <c r="W14">
+        <v>1</v>
+      </c>
+      <c r="X14">
+        <v>1</v>
+      </c>
+      <c r="Y14">
+        <v>1</v>
+      </c>
+      <c r="Z14">
+        <v>1</v>
+      </c>
+      <c r="AA14">
+        <v>1</v>
+      </c>
+      <c r="AB14">
+        <v>1</v>
+      </c>
+      <c r="AC14">
+        <v>1</v>
+      </c>
+      <c r="AD14">
+        <v>1</v>
+      </c>
+      <c r="AE14">
+        <v>1</v>
+      </c>
+      <c r="AF14">
+        <v>1</v>
+      </c>
+      <c r="AG14">
+        <v>1</v>
+      </c>
+      <c r="AH14">
+        <v>1</v>
+      </c>
+      <c r="AI14">
+        <v>1</v>
+      </c>
+      <c r="AJ14">
+        <v>1</v>
+      </c>
+      <c r="AK14">
+        <v>1</v>
+      </c>
+      <c r="AL14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:38">
+      <c r="A15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" t="s">
+        <v>34</v>
+      </c>
+      <c r="E15" t="s">
+        <v>41</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="L15">
+        <v>1</v>
+      </c>
+      <c r="M15">
+        <v>1</v>
+      </c>
+      <c r="N15">
+        <v>1</v>
+      </c>
+      <c r="O15">
+        <v>1</v>
+      </c>
+      <c r="P15">
+        <v>1</v>
+      </c>
+      <c r="Q15">
+        <v>1</v>
+      </c>
+      <c r="R15">
+        <v>1</v>
+      </c>
+      <c r="S15">
+        <v>1</v>
+      </c>
+      <c r="T15">
+        <v>1</v>
+      </c>
+      <c r="U15">
+        <v>1</v>
+      </c>
+      <c r="V15">
+        <v>1</v>
+      </c>
+      <c r="W15">
+        <v>1</v>
+      </c>
+      <c r="X15">
+        <v>1</v>
+      </c>
+      <c r="Y15">
+        <v>1</v>
+      </c>
+      <c r="Z15">
+        <v>1</v>
+      </c>
+      <c r="AA15">
+        <v>1</v>
+      </c>
+      <c r="AB15">
+        <v>1</v>
+      </c>
+      <c r="AC15">
+        <v>1</v>
+      </c>
+      <c r="AD15">
+        <v>1</v>
+      </c>
+      <c r="AE15">
+        <v>1</v>
+      </c>
+      <c r="AF15">
+        <v>1</v>
+      </c>
+      <c r="AG15">
+        <v>1</v>
+      </c>
+      <c r="AH15">
+        <v>1</v>
+      </c>
+      <c r="AI15">
+        <v>1</v>
+      </c>
+      <c r="AJ15">
+        <v>1</v>
+      </c>
+      <c r="AK15">
+        <v>1</v>
+      </c>
+      <c r="AL15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:38">
+      <c r="A16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E16" t="s">
+        <v>41</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+      <c r="J16">
+        <v>1</v>
+      </c>
+      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="L16">
+        <v>1</v>
+      </c>
+      <c r="M16">
+        <v>1</v>
+      </c>
+      <c r="N16">
+        <v>1</v>
+      </c>
+      <c r="O16">
+        <v>1</v>
+      </c>
+      <c r="P16">
+        <v>1</v>
+      </c>
+      <c r="Q16">
+        <v>1</v>
+      </c>
+      <c r="R16">
+        <v>1</v>
+      </c>
+      <c r="S16">
+        <v>1</v>
+      </c>
+      <c r="T16">
+        <v>1</v>
+      </c>
+      <c r="U16">
+        <v>1</v>
+      </c>
+      <c r="V16">
+        <v>1</v>
+      </c>
+      <c r="W16">
+        <v>1</v>
+      </c>
+      <c r="X16">
+        <v>1</v>
+      </c>
+      <c r="Y16">
+        <v>1</v>
+      </c>
+      <c r="Z16">
+        <v>1</v>
+      </c>
+      <c r="AA16">
+        <v>1</v>
+      </c>
+      <c r="AB16">
+        <v>1</v>
+      </c>
+      <c r="AC16">
+        <v>1</v>
+      </c>
+      <c r="AD16">
+        <v>1</v>
+      </c>
+      <c r="AE16">
+        <v>1</v>
+      </c>
+      <c r="AF16">
+        <v>1</v>
+      </c>
+      <c r="AG16">
+        <v>1</v>
+      </c>
+      <c r="AH16">
+        <v>1</v>
+      </c>
+      <c r="AI16">
+        <v>1</v>
+      </c>
+      <c r="AJ16">
+        <v>1</v>
+      </c>
+      <c r="AK16">
+        <v>1</v>
+      </c>
+      <c r="AL16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:38">
+      <c r="A17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E17" t="s">
+        <v>41</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17">
+        <v>1</v>
+      </c>
+      <c r="I17">
+        <v>1</v>
+      </c>
+      <c r="J17">
+        <v>1</v>
+      </c>
+      <c r="K17">
+        <v>1</v>
+      </c>
+      <c r="L17">
+        <v>1</v>
+      </c>
+      <c r="M17">
+        <v>1</v>
+      </c>
+      <c r="N17">
+        <v>1</v>
+      </c>
+      <c r="O17">
+        <v>1</v>
+      </c>
+      <c r="P17">
+        <v>1</v>
+      </c>
+      <c r="Q17">
+        <v>1</v>
+      </c>
+      <c r="R17">
+        <v>1</v>
+      </c>
+      <c r="S17">
+        <v>1</v>
+      </c>
+      <c r="T17">
+        <v>1</v>
+      </c>
+      <c r="U17">
+        <v>1</v>
+      </c>
+      <c r="V17">
+        <v>1</v>
+      </c>
+      <c r="W17">
+        <v>1</v>
+      </c>
+      <c r="X17">
+        <v>1</v>
+      </c>
+      <c r="Y17">
+        <v>1</v>
+      </c>
+      <c r="Z17">
+        <v>1</v>
+      </c>
+      <c r="AA17">
+        <v>1</v>
+      </c>
+      <c r="AB17">
+        <v>1</v>
+      </c>
+      <c r="AC17">
+        <v>1</v>
+      </c>
+      <c r="AD17">
+        <v>1</v>
+      </c>
+      <c r="AE17">
+        <v>1</v>
+      </c>
+      <c r="AF17">
+        <v>1</v>
+      </c>
+      <c r="AG17">
+        <v>1</v>
+      </c>
+      <c r="AH17">
+        <v>1</v>
+      </c>
+      <c r="AI17">
+        <v>1</v>
+      </c>
+      <c r="AJ17">
+        <v>1</v>
+      </c>
+      <c r="AK17">
+        <v>1</v>
+      </c>
+      <c r="AL17">
         <v>1</v>
       </c>
     </row>
@@ -924,19 +2788,19 @@
     </row>
     <row r="2" spans="1:38">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -1040,19 +2904,19 @@
     </row>
     <row r="3" spans="1:38">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="C3" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -1156,19 +3020,19 @@
     </row>
     <row r="4" spans="1:38">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="F4">
         <v>0.6909999999999999</v>
@@ -1272,19 +3136,19 @@
     </row>
     <row r="5" spans="1:38">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -1388,19 +3252,19 @@
     </row>
     <row r="6" spans="1:38">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="C6" t="s">
         <v>6</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="E6" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="F6">
         <v>0.309</v>
@@ -1509,7 +3373,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AL3"/>
+  <dimension ref="A1:AL29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:38">
@@ -1630,16 +3494,16 @@
     </row>
     <row r="2" spans="1:38">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -1743,375 +3607,3098 @@
     </row>
     <row r="3" spans="1:38">
       <c r="A3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+      <c r="N3">
+        <v>1</v>
+      </c>
+      <c r="O3">
+        <v>1</v>
+      </c>
+      <c r="P3">
+        <v>1</v>
+      </c>
+      <c r="Q3">
+        <v>1</v>
+      </c>
+      <c r="R3">
+        <v>1</v>
+      </c>
+      <c r="S3">
+        <v>1</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
+      </c>
+      <c r="U3">
+        <v>1</v>
+      </c>
+      <c r="V3">
+        <v>1</v>
+      </c>
+      <c r="W3">
+        <v>1</v>
+      </c>
+      <c r="X3">
+        <v>1</v>
+      </c>
+      <c r="Y3">
+        <v>1</v>
+      </c>
+      <c r="Z3">
+        <v>1</v>
+      </c>
+      <c r="AA3">
+        <v>1</v>
+      </c>
+      <c r="AB3">
+        <v>1</v>
+      </c>
+      <c r="AC3">
+        <v>1</v>
+      </c>
+      <c r="AD3">
+        <v>1</v>
+      </c>
+      <c r="AE3">
+        <v>1</v>
+      </c>
+      <c r="AF3">
+        <v>1</v>
+      </c>
+      <c r="AG3">
+        <v>1</v>
+      </c>
+      <c r="AH3">
+        <v>1</v>
+      </c>
+      <c r="AI3">
+        <v>1</v>
+      </c>
+      <c r="AJ3">
+        <v>1</v>
+      </c>
+      <c r="AK3">
+        <v>1</v>
+      </c>
+      <c r="AL3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:38">
+      <c r="A4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+      <c r="N4">
+        <v>1</v>
+      </c>
+      <c r="O4">
+        <v>1</v>
+      </c>
+      <c r="P4">
+        <v>1</v>
+      </c>
+      <c r="Q4">
+        <v>1</v>
+      </c>
+      <c r="R4">
+        <v>1</v>
+      </c>
+      <c r="S4">
+        <v>1</v>
+      </c>
+      <c r="T4">
+        <v>1</v>
+      </c>
+      <c r="U4">
+        <v>1</v>
+      </c>
+      <c r="V4">
+        <v>1</v>
+      </c>
+      <c r="W4">
+        <v>1</v>
+      </c>
+      <c r="X4">
+        <v>1</v>
+      </c>
+      <c r="Y4">
+        <v>1</v>
+      </c>
+      <c r="Z4">
+        <v>1</v>
+      </c>
+      <c r="AA4">
+        <v>1</v>
+      </c>
+      <c r="AB4">
+        <v>1</v>
+      </c>
+      <c r="AC4">
+        <v>1</v>
+      </c>
+      <c r="AD4">
+        <v>1</v>
+      </c>
+      <c r="AE4">
+        <v>1</v>
+      </c>
+      <c r="AF4">
+        <v>1</v>
+      </c>
+      <c r="AG4">
+        <v>1</v>
+      </c>
+      <c r="AH4">
+        <v>1</v>
+      </c>
+      <c r="AI4">
+        <v>1</v>
+      </c>
+      <c r="AJ4">
+        <v>1</v>
+      </c>
+      <c r="AK4">
+        <v>1</v>
+      </c>
+      <c r="AL4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:38">
+      <c r="A5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D5" t="s">
+        <v>91</v>
+      </c>
+      <c r="E5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+      <c r="N5">
+        <v>1</v>
+      </c>
+      <c r="O5">
+        <v>1</v>
+      </c>
+      <c r="P5">
+        <v>1</v>
+      </c>
+      <c r="Q5">
+        <v>1</v>
+      </c>
+      <c r="R5">
+        <v>1</v>
+      </c>
+      <c r="S5">
+        <v>1</v>
+      </c>
+      <c r="T5">
+        <v>1</v>
+      </c>
+      <c r="U5">
+        <v>1</v>
+      </c>
+      <c r="V5">
+        <v>1</v>
+      </c>
+      <c r="W5">
+        <v>1</v>
+      </c>
+      <c r="X5">
+        <v>1</v>
+      </c>
+      <c r="Y5">
+        <v>1</v>
+      </c>
+      <c r="Z5">
+        <v>1</v>
+      </c>
+      <c r="AA5">
+        <v>1</v>
+      </c>
+      <c r="AB5">
+        <v>1</v>
+      </c>
+      <c r="AC5">
+        <v>1</v>
+      </c>
+      <c r="AD5">
+        <v>1</v>
+      </c>
+      <c r="AE5">
+        <v>1</v>
+      </c>
+      <c r="AF5">
+        <v>1</v>
+      </c>
+      <c r="AG5">
+        <v>1</v>
+      </c>
+      <c r="AH5">
+        <v>1</v>
+      </c>
+      <c r="AI5">
+        <v>1</v>
+      </c>
+      <c r="AJ5">
+        <v>1</v>
+      </c>
+      <c r="AK5">
+        <v>1</v>
+      </c>
+      <c r="AL5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:38">
+      <c r="A6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="P6">
+        <v>1</v>
+      </c>
+      <c r="Q6">
+        <v>1</v>
+      </c>
+      <c r="R6">
+        <v>1</v>
+      </c>
+      <c r="S6">
+        <v>1</v>
+      </c>
+      <c r="T6">
+        <v>1</v>
+      </c>
+      <c r="U6">
+        <v>1</v>
+      </c>
+      <c r="V6">
+        <v>1</v>
+      </c>
+      <c r="W6">
+        <v>1</v>
+      </c>
+      <c r="X6">
+        <v>1</v>
+      </c>
+      <c r="Y6">
+        <v>1</v>
+      </c>
+      <c r="Z6">
+        <v>1</v>
+      </c>
+      <c r="AA6">
+        <v>1</v>
+      </c>
+      <c r="AB6">
+        <v>1</v>
+      </c>
+      <c r="AC6">
+        <v>1</v>
+      </c>
+      <c r="AD6">
+        <v>1</v>
+      </c>
+      <c r="AE6">
+        <v>1</v>
+      </c>
+      <c r="AF6">
+        <v>1</v>
+      </c>
+      <c r="AG6">
+        <v>1</v>
+      </c>
+      <c r="AH6">
+        <v>1</v>
+      </c>
+      <c r="AI6">
+        <v>1</v>
+      </c>
+      <c r="AJ6">
+        <v>1</v>
+      </c>
+      <c r="AK6">
+        <v>1</v>
+      </c>
+      <c r="AL6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:38">
+      <c r="A7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D7" t="s">
+        <v>92</v>
+      </c>
+      <c r="E7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+      <c r="N7">
+        <v>1</v>
+      </c>
+      <c r="O7">
+        <v>1</v>
+      </c>
+      <c r="P7">
+        <v>1</v>
+      </c>
+      <c r="Q7">
+        <v>1</v>
+      </c>
+      <c r="R7">
+        <v>1</v>
+      </c>
+      <c r="S7">
+        <v>1</v>
+      </c>
+      <c r="T7">
+        <v>1</v>
+      </c>
+      <c r="U7">
+        <v>1</v>
+      </c>
+      <c r="V7">
+        <v>1</v>
+      </c>
+      <c r="W7">
+        <v>1</v>
+      </c>
+      <c r="X7">
+        <v>1</v>
+      </c>
+      <c r="Y7">
+        <v>1</v>
+      </c>
+      <c r="Z7">
+        <v>1</v>
+      </c>
+      <c r="AA7">
+        <v>1</v>
+      </c>
+      <c r="AB7">
+        <v>1</v>
+      </c>
+      <c r="AC7">
+        <v>1</v>
+      </c>
+      <c r="AD7">
+        <v>1</v>
+      </c>
+      <c r="AE7">
+        <v>1</v>
+      </c>
+      <c r="AF7">
+        <v>1</v>
+      </c>
+      <c r="AG7">
+        <v>1</v>
+      </c>
+      <c r="AH7">
+        <v>1</v>
+      </c>
+      <c r="AI7">
+        <v>1</v>
+      </c>
+      <c r="AJ7">
+        <v>1</v>
+      </c>
+      <c r="AK7">
+        <v>1</v>
+      </c>
+      <c r="AL7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:38">
+      <c r="A8" t="s">
+        <v>51</v>
+      </c>
+      <c r="B8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <v>1</v>
+      </c>
+      <c r="N8">
+        <v>1</v>
+      </c>
+      <c r="O8">
+        <v>1</v>
+      </c>
+      <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="Q8">
+        <v>1</v>
+      </c>
+      <c r="R8">
+        <v>1</v>
+      </c>
+      <c r="S8">
+        <v>1</v>
+      </c>
+      <c r="T8">
+        <v>1</v>
+      </c>
+      <c r="U8">
+        <v>1</v>
+      </c>
+      <c r="V8">
+        <v>1</v>
+      </c>
+      <c r="W8">
+        <v>1</v>
+      </c>
+      <c r="X8">
+        <v>1</v>
+      </c>
+      <c r="Y8">
+        <v>1</v>
+      </c>
+      <c r="Z8">
+        <v>1</v>
+      </c>
+      <c r="AA8">
+        <v>1</v>
+      </c>
+      <c r="AB8">
+        <v>1</v>
+      </c>
+      <c r="AC8">
+        <v>1</v>
+      </c>
+      <c r="AD8">
+        <v>1</v>
+      </c>
+      <c r="AE8">
+        <v>1</v>
+      </c>
+      <c r="AF8">
+        <v>1</v>
+      </c>
+      <c r="AG8">
+        <v>1</v>
+      </c>
+      <c r="AH8">
+        <v>1</v>
+      </c>
+      <c r="AI8">
+        <v>1</v>
+      </c>
+      <c r="AJ8">
+        <v>1</v>
+      </c>
+      <c r="AK8">
+        <v>1</v>
+      </c>
+      <c r="AL8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:38">
+      <c r="A9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D9" t="s">
+        <v>93</v>
+      </c>
+      <c r="E9" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>1</v>
+      </c>
+      <c r="M9">
+        <v>1</v>
+      </c>
+      <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="O9">
+        <v>1</v>
+      </c>
+      <c r="P9">
+        <v>1</v>
+      </c>
+      <c r="Q9">
+        <v>1</v>
+      </c>
+      <c r="R9">
+        <v>1</v>
+      </c>
+      <c r="S9">
+        <v>1</v>
+      </c>
+      <c r="T9">
+        <v>1</v>
+      </c>
+      <c r="U9">
+        <v>1</v>
+      </c>
+      <c r="V9">
+        <v>1</v>
+      </c>
+      <c r="W9">
+        <v>1</v>
+      </c>
+      <c r="X9">
+        <v>1</v>
+      </c>
+      <c r="Y9">
+        <v>1</v>
+      </c>
+      <c r="Z9">
+        <v>1</v>
+      </c>
+      <c r="AA9">
+        <v>1</v>
+      </c>
+      <c r="AB9">
+        <v>1</v>
+      </c>
+      <c r="AC9">
+        <v>1</v>
+      </c>
+      <c r="AD9">
+        <v>1</v>
+      </c>
+      <c r="AE9">
+        <v>1</v>
+      </c>
+      <c r="AF9">
+        <v>1</v>
+      </c>
+      <c r="AG9">
+        <v>1</v>
+      </c>
+      <c r="AH9">
+        <v>1</v>
+      </c>
+      <c r="AI9">
+        <v>1</v>
+      </c>
+      <c r="AJ9">
+        <v>1</v>
+      </c>
+      <c r="AK9">
+        <v>1</v>
+      </c>
+      <c r="AL9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:38">
+      <c r="A10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>47</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="M10">
+        <v>1</v>
+      </c>
+      <c r="N10">
+        <v>1</v>
+      </c>
+      <c r="O10">
+        <v>1</v>
+      </c>
+      <c r="P10">
+        <v>1</v>
+      </c>
+      <c r="Q10">
+        <v>1</v>
+      </c>
+      <c r="R10">
+        <v>1</v>
+      </c>
+      <c r="S10">
+        <v>1</v>
+      </c>
+      <c r="T10">
+        <v>1</v>
+      </c>
+      <c r="U10">
+        <v>1</v>
+      </c>
+      <c r="V10">
+        <v>1</v>
+      </c>
+      <c r="W10">
+        <v>1</v>
+      </c>
+      <c r="X10">
+        <v>1</v>
+      </c>
+      <c r="Y10">
+        <v>1</v>
+      </c>
+      <c r="Z10">
+        <v>1</v>
+      </c>
+      <c r="AA10">
+        <v>1</v>
+      </c>
+      <c r="AB10">
+        <v>1</v>
+      </c>
+      <c r="AC10">
+        <v>1</v>
+      </c>
+      <c r="AD10">
+        <v>1</v>
+      </c>
+      <c r="AE10">
+        <v>1</v>
+      </c>
+      <c r="AF10">
+        <v>1</v>
+      </c>
+      <c r="AG10">
+        <v>1</v>
+      </c>
+      <c r="AH10">
+        <v>1</v>
+      </c>
+      <c r="AI10">
+        <v>1</v>
+      </c>
+      <c r="AJ10">
+        <v>1</v>
+      </c>
+      <c r="AK10">
+        <v>1</v>
+      </c>
+      <c r="AL10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:38">
+      <c r="A11" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" t="s">
+        <v>66</v>
+      </c>
+      <c r="C11" t="s">
+        <v>80</v>
+      </c>
+      <c r="D11" t="s">
+        <v>94</v>
+      </c>
+      <c r="E11" t="s">
+        <v>41</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
+      <c r="M11">
+        <v>1</v>
+      </c>
+      <c r="N11">
+        <v>1</v>
+      </c>
+      <c r="O11">
+        <v>1</v>
+      </c>
+      <c r="P11">
+        <v>1</v>
+      </c>
+      <c r="Q11">
+        <v>1</v>
+      </c>
+      <c r="R11">
+        <v>1</v>
+      </c>
+      <c r="S11">
+        <v>1</v>
+      </c>
+      <c r="T11">
+        <v>1</v>
+      </c>
+      <c r="U11">
+        <v>1</v>
+      </c>
+      <c r="V11">
+        <v>1</v>
+      </c>
+      <c r="W11">
+        <v>1</v>
+      </c>
+      <c r="X11">
+        <v>1</v>
+      </c>
+      <c r="Y11">
+        <v>1</v>
+      </c>
+      <c r="Z11">
+        <v>1</v>
+      </c>
+      <c r="AA11">
+        <v>1</v>
+      </c>
+      <c r="AB11">
+        <v>1</v>
+      </c>
+      <c r="AC11">
+        <v>1</v>
+      </c>
+      <c r="AD11">
+        <v>1</v>
+      </c>
+      <c r="AE11">
+        <v>1</v>
+      </c>
+      <c r="AF11">
+        <v>1</v>
+      </c>
+      <c r="AG11">
+        <v>1</v>
+      </c>
+      <c r="AH11">
+        <v>1</v>
+      </c>
+      <c r="AI11">
+        <v>1</v>
+      </c>
+      <c r="AJ11">
+        <v>1</v>
+      </c>
+      <c r="AK11">
+        <v>1</v>
+      </c>
+      <c r="AL11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:38">
+      <c r="A12" t="s">
+        <v>53</v>
+      </c>
+      <c r="B12" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" t="s">
+        <v>47</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
+      <c r="M12">
+        <v>1</v>
+      </c>
+      <c r="N12">
+        <v>1</v>
+      </c>
+      <c r="O12">
+        <v>1</v>
+      </c>
+      <c r="P12">
+        <v>1</v>
+      </c>
+      <c r="Q12">
+        <v>1</v>
+      </c>
+      <c r="R12">
+        <v>1</v>
+      </c>
+      <c r="S12">
+        <v>1</v>
+      </c>
+      <c r="T12">
+        <v>1</v>
+      </c>
+      <c r="U12">
+        <v>1</v>
+      </c>
+      <c r="V12">
+        <v>1</v>
+      </c>
+      <c r="W12">
+        <v>1</v>
+      </c>
+      <c r="X12">
+        <v>1</v>
+      </c>
+      <c r="Y12">
+        <v>1</v>
+      </c>
+      <c r="Z12">
+        <v>1</v>
+      </c>
+      <c r="AA12">
+        <v>1</v>
+      </c>
+      <c r="AB12">
+        <v>1</v>
+      </c>
+      <c r="AC12">
+        <v>1</v>
+      </c>
+      <c r="AD12">
+        <v>1</v>
+      </c>
+      <c r="AE12">
+        <v>1</v>
+      </c>
+      <c r="AF12">
+        <v>1</v>
+      </c>
+      <c r="AG12">
+        <v>1</v>
+      </c>
+      <c r="AH12">
+        <v>1</v>
+      </c>
+      <c r="AI12">
+        <v>1</v>
+      </c>
+      <c r="AJ12">
+        <v>1</v>
+      </c>
+      <c r="AK12">
+        <v>1</v>
+      </c>
+      <c r="AL12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:38">
+      <c r="A13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C13" t="s">
+        <v>81</v>
+      </c>
+      <c r="D13" t="s">
+        <v>95</v>
+      </c>
+      <c r="E13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+      <c r="K13">
+        <v>1</v>
+      </c>
+      <c r="L13">
+        <v>1</v>
+      </c>
+      <c r="M13">
+        <v>1</v>
+      </c>
+      <c r="N13">
+        <v>1</v>
+      </c>
+      <c r="O13">
+        <v>1</v>
+      </c>
+      <c r="P13">
+        <v>1</v>
+      </c>
+      <c r="Q13">
+        <v>1</v>
+      </c>
+      <c r="R13">
+        <v>1</v>
+      </c>
+      <c r="S13">
+        <v>1</v>
+      </c>
+      <c r="T13">
+        <v>1</v>
+      </c>
+      <c r="U13">
+        <v>1</v>
+      </c>
+      <c r="V13">
+        <v>1</v>
+      </c>
+      <c r="W13">
+        <v>1</v>
+      </c>
+      <c r="X13">
+        <v>1</v>
+      </c>
+      <c r="Y13">
+        <v>1</v>
+      </c>
+      <c r="Z13">
+        <v>1</v>
+      </c>
+      <c r="AA13">
+        <v>1</v>
+      </c>
+      <c r="AB13">
+        <v>1</v>
+      </c>
+      <c r="AC13">
+        <v>1</v>
+      </c>
+      <c r="AD13">
+        <v>1</v>
+      </c>
+      <c r="AE13">
+        <v>1</v>
+      </c>
+      <c r="AF13">
+        <v>1</v>
+      </c>
+      <c r="AG13">
+        <v>1</v>
+      </c>
+      <c r="AH13">
+        <v>1</v>
+      </c>
+      <c r="AI13">
+        <v>1</v>
+      </c>
+      <c r="AJ13">
+        <v>1</v>
+      </c>
+      <c r="AK13">
+        <v>1</v>
+      </c>
+      <c r="AL13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:38">
+      <c r="A14" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" t="s">
+        <v>68</v>
+      </c>
+      <c r="C14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" t="s">
+        <v>47</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="K14">
+        <v>1</v>
+      </c>
+      <c r="L14">
+        <v>1</v>
+      </c>
+      <c r="M14">
+        <v>1</v>
+      </c>
+      <c r="N14">
+        <v>1</v>
+      </c>
+      <c r="O14">
+        <v>1</v>
+      </c>
+      <c r="P14">
+        <v>1</v>
+      </c>
+      <c r="Q14">
+        <v>1</v>
+      </c>
+      <c r="R14">
+        <v>1</v>
+      </c>
+      <c r="S14">
+        <v>1</v>
+      </c>
+      <c r="T14">
+        <v>1</v>
+      </c>
+      <c r="U14">
+        <v>1</v>
+      </c>
+      <c r="V14">
+        <v>1</v>
+      </c>
+      <c r="W14">
+        <v>1</v>
+      </c>
+      <c r="X14">
+        <v>1</v>
+      </c>
+      <c r="Y14">
+        <v>1</v>
+      </c>
+      <c r="Z14">
+        <v>1</v>
+      </c>
+      <c r="AA14">
+        <v>1</v>
+      </c>
+      <c r="AB14">
+        <v>1</v>
+      </c>
+      <c r="AC14">
+        <v>1</v>
+      </c>
+      <c r="AD14">
+        <v>1</v>
+      </c>
+      <c r="AE14">
+        <v>1</v>
+      </c>
+      <c r="AF14">
+        <v>1</v>
+      </c>
+      <c r="AG14">
+        <v>1</v>
+      </c>
+      <c r="AH14">
+        <v>1</v>
+      </c>
+      <c r="AI14">
+        <v>1</v>
+      </c>
+      <c r="AJ14">
+        <v>1</v>
+      </c>
+      <c r="AK14">
+        <v>1</v>
+      </c>
+      <c r="AL14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:38">
+      <c r="A15" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" t="s">
+        <v>68</v>
+      </c>
+      <c r="C15" t="s">
+        <v>82</v>
+      </c>
+      <c r="D15" t="s">
+        <v>96</v>
+      </c>
+      <c r="E15" t="s">
+        <v>41</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="L15">
+        <v>1</v>
+      </c>
+      <c r="M15">
+        <v>1</v>
+      </c>
+      <c r="N15">
+        <v>1</v>
+      </c>
+      <c r="O15">
+        <v>1</v>
+      </c>
+      <c r="P15">
+        <v>1</v>
+      </c>
+      <c r="Q15">
+        <v>1</v>
+      </c>
+      <c r="R15">
+        <v>1</v>
+      </c>
+      <c r="S15">
+        <v>1</v>
+      </c>
+      <c r="T15">
+        <v>1</v>
+      </c>
+      <c r="U15">
+        <v>1</v>
+      </c>
+      <c r="V15">
+        <v>1</v>
+      </c>
+      <c r="W15">
+        <v>1</v>
+      </c>
+      <c r="X15">
+        <v>1</v>
+      </c>
+      <c r="Y15">
+        <v>1</v>
+      </c>
+      <c r="Z15">
+        <v>1</v>
+      </c>
+      <c r="AA15">
+        <v>1</v>
+      </c>
+      <c r="AB15">
+        <v>1</v>
+      </c>
+      <c r="AC15">
+        <v>1</v>
+      </c>
+      <c r="AD15">
+        <v>1</v>
+      </c>
+      <c r="AE15">
+        <v>1</v>
+      </c>
+      <c r="AF15">
+        <v>1</v>
+      </c>
+      <c r="AG15">
+        <v>1</v>
+      </c>
+      <c r="AH15">
+        <v>1</v>
+      </c>
+      <c r="AI15">
+        <v>1</v>
+      </c>
+      <c r="AJ15">
+        <v>1</v>
+      </c>
+      <c r="AK15">
+        <v>1</v>
+      </c>
+      <c r="AL15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:38">
+      <c r="A16" t="s">
+        <v>55</v>
+      </c>
+      <c r="B16" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" t="s">
+        <v>47</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+      <c r="J16">
+        <v>1</v>
+      </c>
+      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="L16">
+        <v>1</v>
+      </c>
+      <c r="M16">
+        <v>1</v>
+      </c>
+      <c r="N16">
+        <v>1</v>
+      </c>
+      <c r="O16">
+        <v>1</v>
+      </c>
+      <c r="P16">
+        <v>1</v>
+      </c>
+      <c r="Q16">
+        <v>1</v>
+      </c>
+      <c r="R16">
+        <v>1</v>
+      </c>
+      <c r="S16">
+        <v>1</v>
+      </c>
+      <c r="T16">
+        <v>1</v>
+      </c>
+      <c r="U16">
+        <v>1</v>
+      </c>
+      <c r="V16">
+        <v>1</v>
+      </c>
+      <c r="W16">
+        <v>1</v>
+      </c>
+      <c r="X16">
+        <v>1</v>
+      </c>
+      <c r="Y16">
+        <v>1</v>
+      </c>
+      <c r="Z16">
+        <v>1</v>
+      </c>
+      <c r="AA16">
+        <v>1</v>
+      </c>
+      <c r="AB16">
+        <v>1</v>
+      </c>
+      <c r="AC16">
+        <v>1</v>
+      </c>
+      <c r="AD16">
+        <v>1</v>
+      </c>
+      <c r="AE16">
+        <v>1</v>
+      </c>
+      <c r="AF16">
+        <v>1</v>
+      </c>
+      <c r="AG16">
+        <v>1</v>
+      </c>
+      <c r="AH16">
+        <v>1</v>
+      </c>
+      <c r="AI16">
+        <v>1</v>
+      </c>
+      <c r="AJ16">
+        <v>1</v>
+      </c>
+      <c r="AK16">
+        <v>1</v>
+      </c>
+      <c r="AL16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:38">
+      <c r="A17" t="s">
+        <v>55</v>
+      </c>
+      <c r="B17" t="s">
+        <v>69</v>
+      </c>
+      <c r="C17" t="s">
+        <v>83</v>
+      </c>
+      <c r="D17" t="s">
+        <v>97</v>
+      </c>
+      <c r="E17" t="s">
+        <v>41</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17">
+        <v>1</v>
+      </c>
+      <c r="I17">
+        <v>1</v>
+      </c>
+      <c r="J17">
+        <v>1</v>
+      </c>
+      <c r="K17">
+        <v>1</v>
+      </c>
+      <c r="L17">
+        <v>1</v>
+      </c>
+      <c r="M17">
+        <v>1</v>
+      </c>
+      <c r="N17">
+        <v>1</v>
+      </c>
+      <c r="O17">
+        <v>1</v>
+      </c>
+      <c r="P17">
+        <v>1</v>
+      </c>
+      <c r="Q17">
+        <v>1</v>
+      </c>
+      <c r="R17">
+        <v>1</v>
+      </c>
+      <c r="S17">
+        <v>1</v>
+      </c>
+      <c r="T17">
+        <v>1</v>
+      </c>
+      <c r="U17">
+        <v>1</v>
+      </c>
+      <c r="V17">
+        <v>1</v>
+      </c>
+      <c r="W17">
+        <v>1</v>
+      </c>
+      <c r="X17">
+        <v>1</v>
+      </c>
+      <c r="Y17">
+        <v>1</v>
+      </c>
+      <c r="Z17">
+        <v>1</v>
+      </c>
+      <c r="AA17">
+        <v>1</v>
+      </c>
+      <c r="AB17">
+        <v>1</v>
+      </c>
+      <c r="AC17">
+        <v>1</v>
+      </c>
+      <c r="AD17">
+        <v>1</v>
+      </c>
+      <c r="AE17">
+        <v>1</v>
+      </c>
+      <c r="AF17">
+        <v>1</v>
+      </c>
+      <c r="AG17">
+        <v>1</v>
+      </c>
+      <c r="AH17">
+        <v>1</v>
+      </c>
+      <c r="AI17">
+        <v>1</v>
+      </c>
+      <c r="AJ17">
+        <v>1</v>
+      </c>
+      <c r="AK17">
+        <v>1</v>
+      </c>
+      <c r="AL17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:38">
+      <c r="A18" t="s">
+        <v>56</v>
+      </c>
+      <c r="B18" t="s">
+        <v>70</v>
+      </c>
+      <c r="C18" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18" t="s">
+        <v>47</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="L18">
+        <v>1</v>
+      </c>
+      <c r="M18">
+        <v>1</v>
+      </c>
+      <c r="N18">
+        <v>1</v>
+      </c>
+      <c r="O18">
+        <v>1</v>
+      </c>
+      <c r="P18">
+        <v>1</v>
+      </c>
+      <c r="Q18">
+        <v>1</v>
+      </c>
+      <c r="R18">
+        <v>1</v>
+      </c>
+      <c r="S18">
+        <v>1</v>
+      </c>
+      <c r="T18">
+        <v>1</v>
+      </c>
+      <c r="U18">
+        <v>1</v>
+      </c>
+      <c r="V18">
+        <v>1</v>
+      </c>
+      <c r="W18">
+        <v>1</v>
+      </c>
+      <c r="X18">
+        <v>1</v>
+      </c>
+      <c r="Y18">
+        <v>1</v>
+      </c>
+      <c r="Z18">
+        <v>1</v>
+      </c>
+      <c r="AA18">
+        <v>1</v>
+      </c>
+      <c r="AB18">
+        <v>1</v>
+      </c>
+      <c r="AC18">
+        <v>1</v>
+      </c>
+      <c r="AD18">
+        <v>1</v>
+      </c>
+      <c r="AE18">
+        <v>1</v>
+      </c>
+      <c r="AF18">
+        <v>1</v>
+      </c>
+      <c r="AG18">
+        <v>1</v>
+      </c>
+      <c r="AH18">
+        <v>1</v>
+      </c>
+      <c r="AI18">
+        <v>1</v>
+      </c>
+      <c r="AJ18">
+        <v>1</v>
+      </c>
+      <c r="AK18">
+        <v>1</v>
+      </c>
+      <c r="AL18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:38">
+      <c r="A19" t="s">
+        <v>56</v>
+      </c>
+      <c r="B19" t="s">
+        <v>70</v>
+      </c>
+      <c r="C19" t="s">
+        <v>84</v>
+      </c>
+      <c r="D19" t="s">
+        <v>98</v>
+      </c>
+      <c r="E19" t="s">
+        <v>41</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+      <c r="I19">
+        <v>1</v>
+      </c>
+      <c r="J19">
+        <v>1</v>
+      </c>
+      <c r="K19">
+        <v>1</v>
+      </c>
+      <c r="L19">
+        <v>1</v>
+      </c>
+      <c r="M19">
+        <v>1</v>
+      </c>
+      <c r="N19">
+        <v>1</v>
+      </c>
+      <c r="O19">
+        <v>1</v>
+      </c>
+      <c r="P19">
+        <v>1</v>
+      </c>
+      <c r="Q19">
+        <v>1</v>
+      </c>
+      <c r="R19">
+        <v>1</v>
+      </c>
+      <c r="S19">
+        <v>1</v>
+      </c>
+      <c r="T19">
+        <v>1</v>
+      </c>
+      <c r="U19">
+        <v>1</v>
+      </c>
+      <c r="V19">
+        <v>1</v>
+      </c>
+      <c r="W19">
+        <v>1</v>
+      </c>
+      <c r="X19">
+        <v>1</v>
+      </c>
+      <c r="Y19">
+        <v>1</v>
+      </c>
+      <c r="Z19">
+        <v>1</v>
+      </c>
+      <c r="AA19">
+        <v>1</v>
+      </c>
+      <c r="AB19">
+        <v>1</v>
+      </c>
+      <c r="AC19">
+        <v>1</v>
+      </c>
+      <c r="AD19">
+        <v>1</v>
+      </c>
+      <c r="AE19">
+        <v>1</v>
+      </c>
+      <c r="AF19">
+        <v>1</v>
+      </c>
+      <c r="AG19">
+        <v>1</v>
+      </c>
+      <c r="AH19">
+        <v>1</v>
+      </c>
+      <c r="AI19">
+        <v>1</v>
+      </c>
+      <c r="AJ19">
+        <v>1</v>
+      </c>
+      <c r="AK19">
+        <v>1</v>
+      </c>
+      <c r="AL19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:38">
+      <c r="A20" t="s">
+        <v>57</v>
+      </c>
+      <c r="B20" t="s">
+        <v>71</v>
+      </c>
+      <c r="C20" t="s">
+        <v>16</v>
+      </c>
+      <c r="E20" t="s">
+        <v>47</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20">
+        <v>1</v>
+      </c>
+      <c r="I20">
+        <v>1</v>
+      </c>
+      <c r="J20">
+        <v>1</v>
+      </c>
+      <c r="K20">
+        <v>1</v>
+      </c>
+      <c r="L20">
+        <v>1</v>
+      </c>
+      <c r="M20">
+        <v>1</v>
+      </c>
+      <c r="N20">
+        <v>1</v>
+      </c>
+      <c r="O20">
+        <v>1</v>
+      </c>
+      <c r="P20">
+        <v>1</v>
+      </c>
+      <c r="Q20">
+        <v>1</v>
+      </c>
+      <c r="R20">
+        <v>1</v>
+      </c>
+      <c r="S20">
+        <v>1</v>
+      </c>
+      <c r="T20">
+        <v>1</v>
+      </c>
+      <c r="U20">
+        <v>1</v>
+      </c>
+      <c r="V20">
+        <v>1</v>
+      </c>
+      <c r="W20">
+        <v>1</v>
+      </c>
+      <c r="X20">
+        <v>1</v>
+      </c>
+      <c r="Y20">
+        <v>1</v>
+      </c>
+      <c r="Z20">
+        <v>1</v>
+      </c>
+      <c r="AA20">
+        <v>1</v>
+      </c>
+      <c r="AB20">
+        <v>1</v>
+      </c>
+      <c r="AC20">
+        <v>1</v>
+      </c>
+      <c r="AD20">
+        <v>1</v>
+      </c>
+      <c r="AE20">
+        <v>1</v>
+      </c>
+      <c r="AF20">
+        <v>1</v>
+      </c>
+      <c r="AG20">
+        <v>1</v>
+      </c>
+      <c r="AH20">
+        <v>1</v>
+      </c>
+      <c r="AI20">
+        <v>1</v>
+      </c>
+      <c r="AJ20">
+        <v>1</v>
+      </c>
+      <c r="AK20">
+        <v>1</v>
+      </c>
+      <c r="AL20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:38">
+      <c r="A21" t="s">
+        <v>57</v>
+      </c>
+      <c r="B21" t="s">
+        <v>71</v>
+      </c>
+      <c r="C21" t="s">
+        <v>85</v>
+      </c>
+      <c r="D21" t="s">
+        <v>99</v>
+      </c>
+      <c r="E21" t="s">
+        <v>41</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="I21">
+        <v>1</v>
+      </c>
+      <c r="J21">
+        <v>1</v>
+      </c>
+      <c r="K21">
+        <v>1</v>
+      </c>
+      <c r="L21">
+        <v>1</v>
+      </c>
+      <c r="M21">
+        <v>1</v>
+      </c>
+      <c r="N21">
+        <v>1</v>
+      </c>
+      <c r="O21">
+        <v>1</v>
+      </c>
+      <c r="P21">
+        <v>1</v>
+      </c>
+      <c r="Q21">
+        <v>1</v>
+      </c>
+      <c r="R21">
+        <v>1</v>
+      </c>
+      <c r="S21">
+        <v>1</v>
+      </c>
+      <c r="T21">
+        <v>1</v>
+      </c>
+      <c r="U21">
+        <v>1</v>
+      </c>
+      <c r="V21">
+        <v>1</v>
+      </c>
+      <c r="W21">
+        <v>1</v>
+      </c>
+      <c r="X21">
+        <v>1</v>
+      </c>
+      <c r="Y21">
+        <v>1</v>
+      </c>
+      <c r="Z21">
+        <v>1</v>
+      </c>
+      <c r="AA21">
+        <v>1</v>
+      </c>
+      <c r="AB21">
+        <v>1</v>
+      </c>
+      <c r="AC21">
+        <v>1</v>
+      </c>
+      <c r="AD21">
+        <v>1</v>
+      </c>
+      <c r="AE21">
+        <v>1</v>
+      </c>
+      <c r="AF21">
+        <v>1</v>
+      </c>
+      <c r="AG21">
+        <v>1</v>
+      </c>
+      <c r="AH21">
+        <v>1</v>
+      </c>
+      <c r="AI21">
+        <v>1</v>
+      </c>
+      <c r="AJ21">
+        <v>1</v>
+      </c>
+      <c r="AK21">
+        <v>1</v>
+      </c>
+      <c r="AL21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:38">
+      <c r="A22" t="s">
+        <v>58</v>
+      </c>
+      <c r="B22" t="s">
+        <v>72</v>
+      </c>
+      <c r="C22" t="s">
+        <v>17</v>
+      </c>
+      <c r="E22" t="s">
+        <v>47</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22">
+        <v>1</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
+      <c r="J22">
+        <v>1</v>
+      </c>
+      <c r="K22">
+        <v>1</v>
+      </c>
+      <c r="L22">
+        <v>1</v>
+      </c>
+      <c r="M22">
+        <v>1</v>
+      </c>
+      <c r="N22">
+        <v>1</v>
+      </c>
+      <c r="O22">
+        <v>1</v>
+      </c>
+      <c r="P22">
+        <v>1</v>
+      </c>
+      <c r="Q22">
+        <v>1</v>
+      </c>
+      <c r="R22">
+        <v>1</v>
+      </c>
+      <c r="S22">
+        <v>1</v>
+      </c>
+      <c r="T22">
+        <v>1</v>
+      </c>
+      <c r="U22">
+        <v>1</v>
+      </c>
+      <c r="V22">
+        <v>1</v>
+      </c>
+      <c r="W22">
+        <v>1</v>
+      </c>
+      <c r="X22">
+        <v>1</v>
+      </c>
+      <c r="Y22">
+        <v>1</v>
+      </c>
+      <c r="Z22">
+        <v>1</v>
+      </c>
+      <c r="AA22">
+        <v>1</v>
+      </c>
+      <c r="AB22">
+        <v>1</v>
+      </c>
+      <c r="AC22">
+        <v>1</v>
+      </c>
+      <c r="AD22">
+        <v>1</v>
+      </c>
+      <c r="AE22">
+        <v>1</v>
+      </c>
+      <c r="AF22">
+        <v>1</v>
+      </c>
+      <c r="AG22">
+        <v>1</v>
+      </c>
+      <c r="AH22">
+        <v>1</v>
+      </c>
+      <c r="AI22">
+        <v>1</v>
+      </c>
+      <c r="AJ22">
+        <v>1</v>
+      </c>
+      <c r="AK22">
+        <v>1</v>
+      </c>
+      <c r="AL22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:38">
+      <c r="A23" t="s">
+        <v>58</v>
+      </c>
+      <c r="B23" t="s">
+        <v>72</v>
+      </c>
+      <c r="C23" t="s">
+        <v>86</v>
+      </c>
+      <c r="D23" t="s">
+        <v>100</v>
+      </c>
+      <c r="E23" t="s">
+        <v>41</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23">
+        <v>1</v>
+      </c>
+      <c r="I23">
+        <v>1</v>
+      </c>
+      <c r="J23">
+        <v>1</v>
+      </c>
+      <c r="K23">
+        <v>1</v>
+      </c>
+      <c r="L23">
+        <v>1</v>
+      </c>
+      <c r="M23">
+        <v>1</v>
+      </c>
+      <c r="N23">
+        <v>1</v>
+      </c>
+      <c r="O23">
+        <v>1</v>
+      </c>
+      <c r="P23">
+        <v>1</v>
+      </c>
+      <c r="Q23">
+        <v>1</v>
+      </c>
+      <c r="R23">
+        <v>1</v>
+      </c>
+      <c r="S23">
+        <v>1</v>
+      </c>
+      <c r="T23">
+        <v>1</v>
+      </c>
+      <c r="U23">
+        <v>1</v>
+      </c>
+      <c r="V23">
+        <v>1</v>
+      </c>
+      <c r="W23">
+        <v>1</v>
+      </c>
+      <c r="X23">
+        <v>1</v>
+      </c>
+      <c r="Y23">
+        <v>1</v>
+      </c>
+      <c r="Z23">
+        <v>1</v>
+      </c>
+      <c r="AA23">
+        <v>1</v>
+      </c>
+      <c r="AB23">
+        <v>1</v>
+      </c>
+      <c r="AC23">
+        <v>1</v>
+      </c>
+      <c r="AD23">
+        <v>1</v>
+      </c>
+      <c r="AE23">
+        <v>1</v>
+      </c>
+      <c r="AF23">
+        <v>1</v>
+      </c>
+      <c r="AG23">
+        <v>1</v>
+      </c>
+      <c r="AH23">
+        <v>1</v>
+      </c>
+      <c r="AI23">
+        <v>1</v>
+      </c>
+      <c r="AJ23">
+        <v>1</v>
+      </c>
+      <c r="AK23">
+        <v>1</v>
+      </c>
+      <c r="AL23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:38">
+      <c r="A24" t="s">
+        <v>59</v>
+      </c>
+      <c r="B24" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24" t="s">
+        <v>18</v>
+      </c>
+      <c r="E24" t="s">
+        <v>47</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+      <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="I24">
+        <v>1</v>
+      </c>
+      <c r="J24">
+        <v>1</v>
+      </c>
+      <c r="K24">
+        <v>1</v>
+      </c>
+      <c r="L24">
+        <v>1</v>
+      </c>
+      <c r="M24">
+        <v>1</v>
+      </c>
+      <c r="N24">
+        <v>1</v>
+      </c>
+      <c r="O24">
+        <v>1</v>
+      </c>
+      <c r="P24">
+        <v>1</v>
+      </c>
+      <c r="Q24">
+        <v>1</v>
+      </c>
+      <c r="R24">
+        <v>1</v>
+      </c>
+      <c r="S24">
+        <v>1</v>
+      </c>
+      <c r="T24">
+        <v>1</v>
+      </c>
+      <c r="U24">
+        <v>1</v>
+      </c>
+      <c r="V24">
+        <v>1</v>
+      </c>
+      <c r="W24">
+        <v>1</v>
+      </c>
+      <c r="X24">
+        <v>1</v>
+      </c>
+      <c r="Y24">
+        <v>1</v>
+      </c>
+      <c r="Z24">
+        <v>1</v>
+      </c>
+      <c r="AA24">
+        <v>1</v>
+      </c>
+      <c r="AB24">
+        <v>1</v>
+      </c>
+      <c r="AC24">
+        <v>1</v>
+      </c>
+      <c r="AD24">
+        <v>1</v>
+      </c>
+      <c r="AE24">
+        <v>1</v>
+      </c>
+      <c r="AF24">
+        <v>1</v>
+      </c>
+      <c r="AG24">
+        <v>1</v>
+      </c>
+      <c r="AH24">
+        <v>1</v>
+      </c>
+      <c r="AI24">
+        <v>1</v>
+      </c>
+      <c r="AJ24">
+        <v>1</v>
+      </c>
+      <c r="AK24">
+        <v>1</v>
+      </c>
+      <c r="AL24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:38">
+      <c r="A25" t="s">
+        <v>59</v>
+      </c>
+      <c r="B25" t="s">
+        <v>73</v>
+      </c>
+      <c r="C25" t="s">
+        <v>87</v>
+      </c>
+      <c r="D25" t="s">
+        <v>101</v>
+      </c>
+      <c r="E25" t="s">
+        <v>41</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+      <c r="H25">
+        <v>1</v>
+      </c>
+      <c r="I25">
+        <v>1</v>
+      </c>
+      <c r="J25">
+        <v>1</v>
+      </c>
+      <c r="K25">
+        <v>1</v>
+      </c>
+      <c r="L25">
+        <v>1</v>
+      </c>
+      <c r="M25">
+        <v>1</v>
+      </c>
+      <c r="N25">
+        <v>1</v>
+      </c>
+      <c r="O25">
+        <v>1</v>
+      </c>
+      <c r="P25">
+        <v>1</v>
+      </c>
+      <c r="Q25">
+        <v>1</v>
+      </c>
+      <c r="R25">
+        <v>1</v>
+      </c>
+      <c r="S25">
+        <v>1</v>
+      </c>
+      <c r="T25">
+        <v>1</v>
+      </c>
+      <c r="U25">
+        <v>1</v>
+      </c>
+      <c r="V25">
+        <v>1</v>
+      </c>
+      <c r="W25">
+        <v>1</v>
+      </c>
+      <c r="X25">
+        <v>1</v>
+      </c>
+      <c r="Y25">
+        <v>1</v>
+      </c>
+      <c r="Z25">
+        <v>1</v>
+      </c>
+      <c r="AA25">
+        <v>1</v>
+      </c>
+      <c r="AB25">
+        <v>1</v>
+      </c>
+      <c r="AC25">
+        <v>1</v>
+      </c>
+      <c r="AD25">
+        <v>1</v>
+      </c>
+      <c r="AE25">
+        <v>1</v>
+      </c>
+      <c r="AF25">
+        <v>1</v>
+      </c>
+      <c r="AG25">
+        <v>1</v>
+      </c>
+      <c r="AH25">
+        <v>1</v>
+      </c>
+      <c r="AI25">
+        <v>1</v>
+      </c>
+      <c r="AJ25">
+        <v>1</v>
+      </c>
+      <c r="AK25">
+        <v>1</v>
+      </c>
+      <c r="AL25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:38">
+      <c r="A26" t="s">
+        <v>60</v>
+      </c>
+      <c r="B26" t="s">
+        <v>74</v>
+      </c>
+      <c r="C26" t="s">
+        <v>19</v>
+      </c>
+      <c r="E26" t="s">
+        <v>47</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+      <c r="H26">
+        <v>1</v>
+      </c>
+      <c r="I26">
+        <v>1</v>
+      </c>
+      <c r="J26">
+        <v>1</v>
+      </c>
+      <c r="K26">
+        <v>1</v>
+      </c>
+      <c r="L26">
+        <v>1</v>
+      </c>
+      <c r="M26">
+        <v>1</v>
+      </c>
+      <c r="N26">
+        <v>1</v>
+      </c>
+      <c r="O26">
+        <v>1</v>
+      </c>
+      <c r="P26">
+        <v>1</v>
+      </c>
+      <c r="Q26">
+        <v>1</v>
+      </c>
+      <c r="R26">
+        <v>1</v>
+      </c>
+      <c r="S26">
+        <v>1</v>
+      </c>
+      <c r="T26">
+        <v>1</v>
+      </c>
+      <c r="U26">
+        <v>1</v>
+      </c>
+      <c r="V26">
+        <v>1</v>
+      </c>
+      <c r="W26">
+        <v>1</v>
+      </c>
+      <c r="X26">
+        <v>1</v>
+      </c>
+      <c r="Y26">
+        <v>1</v>
+      </c>
+      <c r="Z26">
+        <v>1</v>
+      </c>
+      <c r="AA26">
+        <v>1</v>
+      </c>
+      <c r="AB26">
+        <v>1</v>
+      </c>
+      <c r="AC26">
+        <v>1</v>
+      </c>
+      <c r="AD26">
+        <v>1</v>
+      </c>
+      <c r="AE26">
+        <v>1</v>
+      </c>
+      <c r="AF26">
+        <v>1</v>
+      </c>
+      <c r="AG26">
+        <v>1</v>
+      </c>
+      <c r="AH26">
+        <v>1</v>
+      </c>
+      <c r="AI26">
+        <v>1</v>
+      </c>
+      <c r="AJ26">
+        <v>1</v>
+      </c>
+      <c r="AK26">
+        <v>1</v>
+      </c>
+      <c r="AL26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:38">
+      <c r="A27" t="s">
+        <v>60</v>
+      </c>
+      <c r="B27" t="s">
+        <v>74</v>
+      </c>
+      <c r="C27" t="s">
+        <v>88</v>
+      </c>
+      <c r="D27" t="s">
+        <v>102</v>
+      </c>
+      <c r="E27" t="s">
+        <v>41</v>
+      </c>
+      <c r="F27">
+        <v>1</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+      <c r="H27">
+        <v>1</v>
+      </c>
+      <c r="I27">
+        <v>1</v>
+      </c>
+      <c r="J27">
+        <v>1</v>
+      </c>
+      <c r="K27">
+        <v>1</v>
+      </c>
+      <c r="L27">
+        <v>1</v>
+      </c>
+      <c r="M27">
+        <v>1</v>
+      </c>
+      <c r="N27">
+        <v>1</v>
+      </c>
+      <c r="O27">
+        <v>1</v>
+      </c>
+      <c r="P27">
+        <v>1</v>
+      </c>
+      <c r="Q27">
+        <v>1</v>
+      </c>
+      <c r="R27">
+        <v>1</v>
+      </c>
+      <c r="S27">
+        <v>1</v>
+      </c>
+      <c r="T27">
+        <v>1</v>
+      </c>
+      <c r="U27">
+        <v>1</v>
+      </c>
+      <c r="V27">
+        <v>1</v>
+      </c>
+      <c r="W27">
+        <v>1</v>
+      </c>
+      <c r="X27">
+        <v>1</v>
+      </c>
+      <c r="Y27">
+        <v>1</v>
+      </c>
+      <c r="Z27">
+        <v>1</v>
+      </c>
+      <c r="AA27">
+        <v>1</v>
+      </c>
+      <c r="AB27">
+        <v>1</v>
+      </c>
+      <c r="AC27">
+        <v>1</v>
+      </c>
+      <c r="AD27">
+        <v>1</v>
+      </c>
+      <c r="AE27">
+        <v>1</v>
+      </c>
+      <c r="AF27">
+        <v>1</v>
+      </c>
+      <c r="AG27">
+        <v>1</v>
+      </c>
+      <c r="AH27">
+        <v>1</v>
+      </c>
+      <c r="AI27">
+        <v>1</v>
+      </c>
+      <c r="AJ27">
+        <v>1</v>
+      </c>
+      <c r="AK27">
+        <v>1</v>
+      </c>
+      <c r="AL27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:38">
+      <c r="A28" t="s">
+        <v>61</v>
+      </c>
+      <c r="B28" t="s">
+        <v>75</v>
+      </c>
+      <c r="C28" t="s">
         <v>20</v>
       </c>
-      <c r="B3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-      <c r="N3">
-        <v>1</v>
-      </c>
-      <c r="O3">
-        <v>1</v>
-      </c>
-      <c r="P3">
-        <v>1</v>
-      </c>
-      <c r="Q3">
-        <v>1</v>
-      </c>
-      <c r="R3">
-        <v>1</v>
-      </c>
-      <c r="S3">
-        <v>1</v>
-      </c>
-      <c r="T3">
-        <v>1</v>
-      </c>
-      <c r="U3">
-        <v>1</v>
-      </c>
-      <c r="V3">
-        <v>1</v>
-      </c>
-      <c r="W3">
-        <v>1</v>
-      </c>
-      <c r="X3">
-        <v>1</v>
-      </c>
-      <c r="Y3">
-        <v>1</v>
-      </c>
-      <c r="Z3">
-        <v>1</v>
-      </c>
-      <c r="AA3">
-        <v>1</v>
-      </c>
-      <c r="AB3">
-        <v>1</v>
-      </c>
-      <c r="AC3">
-        <v>1</v>
-      </c>
-      <c r="AD3">
-        <v>1</v>
-      </c>
-      <c r="AE3">
-        <v>1</v>
-      </c>
-      <c r="AF3">
-        <v>1</v>
-      </c>
-      <c r="AG3">
-        <v>1</v>
-      </c>
-      <c r="AH3">
-        <v>1</v>
-      </c>
-      <c r="AI3">
-        <v>1</v>
-      </c>
-      <c r="AJ3">
-        <v>1</v>
-      </c>
-      <c r="AK3">
-        <v>1</v>
-      </c>
-      <c r="AL3">
+      <c r="E28" t="s">
+        <v>47</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+      <c r="H28">
+        <v>1</v>
+      </c>
+      <c r="I28">
+        <v>1</v>
+      </c>
+      <c r="J28">
+        <v>1</v>
+      </c>
+      <c r="K28">
+        <v>1</v>
+      </c>
+      <c r="L28">
+        <v>1</v>
+      </c>
+      <c r="M28">
+        <v>1</v>
+      </c>
+      <c r="N28">
+        <v>1</v>
+      </c>
+      <c r="O28">
+        <v>1</v>
+      </c>
+      <c r="P28">
+        <v>1</v>
+      </c>
+      <c r="Q28">
+        <v>1</v>
+      </c>
+      <c r="R28">
+        <v>1</v>
+      </c>
+      <c r="S28">
+        <v>1</v>
+      </c>
+      <c r="T28">
+        <v>1</v>
+      </c>
+      <c r="U28">
+        <v>1</v>
+      </c>
+      <c r="V28">
+        <v>1</v>
+      </c>
+      <c r="W28">
+        <v>1</v>
+      </c>
+      <c r="X28">
+        <v>1</v>
+      </c>
+      <c r="Y28">
+        <v>1</v>
+      </c>
+      <c r="Z28">
+        <v>1</v>
+      </c>
+      <c r="AA28">
+        <v>1</v>
+      </c>
+      <c r="AB28">
+        <v>1</v>
+      </c>
+      <c r="AC28">
+        <v>1</v>
+      </c>
+      <c r="AD28">
+        <v>1</v>
+      </c>
+      <c r="AE28">
+        <v>1</v>
+      </c>
+      <c r="AF28">
+        <v>1</v>
+      </c>
+      <c r="AG28">
+        <v>1</v>
+      </c>
+      <c r="AH28">
+        <v>1</v>
+      </c>
+      <c r="AI28">
+        <v>1</v>
+      </c>
+      <c r="AJ28">
+        <v>1</v>
+      </c>
+      <c r="AK28">
+        <v>1</v>
+      </c>
+      <c r="AL28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:38">
+      <c r="A29" t="s">
+        <v>61</v>
+      </c>
+      <c r="B29" t="s">
+        <v>75</v>
+      </c>
+      <c r="C29" t="s">
+        <v>89</v>
+      </c>
+      <c r="D29" t="s">
+        <v>103</v>
+      </c>
+      <c r="E29" t="s">
+        <v>41</v>
+      </c>
+      <c r="F29">
+        <v>1</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+      <c r="H29">
+        <v>1</v>
+      </c>
+      <c r="I29">
+        <v>1</v>
+      </c>
+      <c r="J29">
+        <v>1</v>
+      </c>
+      <c r="K29">
+        <v>1</v>
+      </c>
+      <c r="L29">
+        <v>1</v>
+      </c>
+      <c r="M29">
+        <v>1</v>
+      </c>
+      <c r="N29">
+        <v>1</v>
+      </c>
+      <c r="O29">
+        <v>1</v>
+      </c>
+      <c r="P29">
+        <v>1</v>
+      </c>
+      <c r="Q29">
+        <v>1</v>
+      </c>
+      <c r="R29">
+        <v>1</v>
+      </c>
+      <c r="S29">
+        <v>1</v>
+      </c>
+      <c r="T29">
+        <v>1</v>
+      </c>
+      <c r="U29">
+        <v>1</v>
+      </c>
+      <c r="V29">
+        <v>1</v>
+      </c>
+      <c r="W29">
+        <v>1</v>
+      </c>
+      <c r="X29">
+        <v>1</v>
+      </c>
+      <c r="Y29">
+        <v>1</v>
+      </c>
+      <c r="Z29">
+        <v>1</v>
+      </c>
+      <c r="AA29">
+        <v>1</v>
+      </c>
+      <c r="AB29">
+        <v>1</v>
+      </c>
+      <c r="AC29">
+        <v>1</v>
+      </c>
+      <c r="AD29">
+        <v>1</v>
+      </c>
+      <c r="AE29">
+        <v>1</v>
+      </c>
+      <c r="AF29">
+        <v>1</v>
+      </c>
+      <c r="AG29">
+        <v>1</v>
+      </c>
+      <c r="AH29">
+        <v>1</v>
+      </c>
+      <c r="AI29">
+        <v>1</v>
+      </c>
+      <c r="AJ29">
+        <v>1</v>
+      </c>
+      <c r="AK29">
+        <v>1</v>
+      </c>
+      <c r="AL29">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000360DE9767CDF0449BF75EAB371D3CB7" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="75cb9a07855af6ac97bd432464ca7c04">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784" xmlns:ns3="081a93ea-d517-42a5-a2b7-457060aa7471" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d1676634304aab9936f6a5a5f53c7423" ns2:_="" ns3:_="">
-    <xsd:import namespace="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784"/>
-    <xsd:import namespace="081a93ea-d517-42a5-a2b7-457060aa7471"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="11" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="71f7bd95-1200-4052-9a4e-dfdf006e181b" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="12" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="13" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="14" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="15" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="16" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="19" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="20" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="21" nillable="true" ma:displayName="Location" ma:description="" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="081a93ea-d517-42a5-a2b7-457060aa7471" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD993230-4FE5-45C7-9EC3-AF0D204DAB7C}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9650DFD-B029-47EA-8AF3-0CD7BEAD820D}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BC966CD-B191-4A41-8665-03A655E03953}"/>
 </file>